--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/data/D3_threshold_library.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/data/D3_threshold_library.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="99">
   <si>
     <t>threshold_id</t>
   </si>
@@ -174,6 +174,18 @@
     <t>T0036</t>
   </si>
   <si>
+    <t>T0037</t>
+  </si>
+  <si>
+    <t>T0038</t>
+  </si>
+  <si>
+    <t>T0039</t>
+  </si>
+  <si>
+    <t>T0040</t>
+  </si>
+  <si>
     <t>DO</t>
   </si>
   <si>
@@ -231,6 +243,12 @@
     <t>all_observed_conditions</t>
   </si>
   <si>
+    <t>hardware_specification</t>
+  </si>
+  <si>
+    <t>observed_values</t>
+  </si>
+  <si>
     <t>contiguous_finite_observations</t>
   </si>
   <si>
@@ -243,6 +261,12 @@
     <t>soft_value</t>
   </si>
   <si>
+    <t>manufacturer_range</t>
+  </si>
+  <si>
+    <t>instrument_veto</t>
+  </si>
+  <si>
     <t>rate_soft</t>
   </si>
   <si>
@@ -267,6 +291,15 @@
     <t>expert</t>
   </si>
   <si>
+    <t>instrument_register</t>
+  </si>
+  <si>
+    <t>registered_range_with_negative_numeric_tolerance</t>
+  </si>
+  <si>
+    <t>registered_range</t>
+  </si>
+  <si>
     <t>benchmark_quantile</t>
   </si>
   <si>
@@ -276,10 +309,10 @@
     <t>benchmark@v2.2.0</t>
   </si>
   <si>
-    <t>fixed_physical_contract_v2.2</t>
-  </si>
-  <si>
-    <t>v2.2.0</t>
+    <t>fixed_physical_contract_v2.2.1</t>
+  </si>
+  <si>
+    <t>v2.2.1</t>
   </si>
 </sst>
 </file>
@@ -637,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -695,16 +728,16 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F2">
         <v>-0.2</v>
@@ -713,22 +746,22 @@
         <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -742,16 +775,16 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -760,22 +793,22 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
@@ -789,43 +822,43 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F4">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
@@ -836,40 +869,40 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F5">
-        <v>-400</v>
+        <v>-0.2</v>
       </c>
       <c r="G5">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I5" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M5" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N5" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
@@ -883,37 +916,40 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>79</v>
+      </c>
+      <c r="F6">
+        <v>-500</v>
       </c>
       <c r="G6">
-        <v>0.15</v>
+        <v>500</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I6" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M6" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N6" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
@@ -927,37 +963,40 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>80</v>
+      </c>
+      <c r="F7">
+        <v>-400</v>
       </c>
       <c r="G7">
-        <v>0.5</v>
+        <v>200</v>
       </c>
       <c r="H7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I7" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N7" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -971,40 +1010,43 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>81</v>
+      </c>
+      <c r="F8">
+        <v>-1500</v>
       </c>
       <c r="G8">
-        <v>8</v>
+        <v>1500</v>
       </c>
       <c r="H8" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I8" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N8" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
@@ -1015,37 +1057,40 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>82</v>
+      </c>
+      <c r="F9">
+        <v>-1500</v>
       </c>
       <c r="G9">
-        <v>25</v>
+        <v>1500</v>
       </c>
       <c r="H9" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I9" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N9" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
@@ -1059,43 +1104,40 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10">
-        <v>0.46</v>
+        <v>83</v>
+      </c>
+      <c r="G10">
+        <v>0.15</v>
       </c>
       <c r="H10" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s">
-        <v>83</v>
-      </c>
-      <c r="J10" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K10">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M10" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N10" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
@@ -1106,43 +1148,40 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G11">
-        <v>2.16</v>
+        <v>0.5</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s">
-        <v>83</v>
-      </c>
-      <c r="J11" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K11">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M11" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N11" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="b">
         <v>1</v>
@@ -1153,43 +1192,40 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12">
-        <v>0.59</v>
+        <v>83</v>
+      </c>
+      <c r="G12">
+        <v>8</v>
       </c>
       <c r="H12" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s">
-        <v>83</v>
-      </c>
-      <c r="J12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K12">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M12" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N12" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="b">
         <v>1</v>
@@ -1200,43 +1236,40 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G13">
-        <v>2.58</v>
+        <v>25</v>
       </c>
       <c r="H13" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I13" t="s">
-        <v>83</v>
-      </c>
-      <c r="J13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K13">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M13" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N13" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" t="b">
         <v>1</v>
@@ -1247,40 +1280,40 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F14">
-        <v>1.15</v>
+        <v>0.46</v>
       </c>
       <c r="H14" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I14" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J14" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K14">
         <v>40</v>
       </c>
       <c r="L14" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M14" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N14" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
@@ -1294,40 +1327,40 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G15">
-        <v>3.95</v>
+        <v>2.16</v>
       </c>
       <c r="H15" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J15" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K15">
         <v>40</v>
       </c>
       <c r="L15" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M15" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N15" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O15" t="b">
         <v>0</v>
@@ -1341,40 +1374,40 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F16">
-        <v>-0.01</v>
+        <v>0.59</v>
       </c>
       <c r="H16" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I16" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J16" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K16">
         <v>40</v>
       </c>
       <c r="L16" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M16" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N16" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O16" t="b">
         <v>0</v>
@@ -1388,40 +1421,40 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G17">
-        <v>0.6</v>
+        <v>2.58</v>
       </c>
       <c r="H17" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I17" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J17" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K17">
         <v>40</v>
       </c>
       <c r="L17" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M17" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N17" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
@@ -1435,40 +1468,40 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F18">
-        <v>0.43</v>
+        <v>1.15</v>
       </c>
       <c r="H18" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I18" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J18" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K18">
         <v>40</v>
       </c>
       <c r="L18" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M18" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N18" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O18" t="b">
         <v>0</v>
@@ -1482,40 +1515,40 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G19">
-        <v>2.13</v>
+        <v>3.95</v>
       </c>
       <c r="H19" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I19" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J19" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K19">
         <v>40</v>
       </c>
       <c r="L19" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M19" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N19" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O19" t="b">
         <v>0</v>
@@ -1529,40 +1562,40 @@
         <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F20">
-        <v>0.5600000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="H20" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I20" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J20" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K20">
         <v>40</v>
       </c>
       <c r="L20" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M20" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N20" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
@@ -1576,40 +1609,40 @@
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G21">
-        <v>2.76</v>
+        <v>0.6</v>
       </c>
       <c r="H21" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I21" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J21" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K21">
         <v>40</v>
       </c>
       <c r="L21" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M21" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N21" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O21" t="b">
         <v>0</v>
@@ -1623,40 +1656,40 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F22">
-        <v>2.26</v>
+        <v>0.43</v>
       </c>
       <c r="H22" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I22" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K22">
         <v>40</v>
       </c>
       <c r="L22" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M22" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N22" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
@@ -1670,40 +1703,40 @@
         <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E23" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G23">
-        <v>5.73</v>
+        <v>2.13</v>
       </c>
       <c r="H23" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I23" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J23" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K23">
         <v>40</v>
       </c>
       <c r="L23" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M23" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N23" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O23" t="b">
         <v>0</v>
@@ -1717,40 +1750,40 @@
         <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E24" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F24">
-        <v>0.04</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H24" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I24" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J24" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K24">
         <v>40</v>
       </c>
       <c r="L24" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M24" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N24" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O24" t="b">
         <v>0</v>
@@ -1764,40 +1797,40 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E25" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G25">
-        <v>0.86</v>
+        <v>2.76</v>
       </c>
       <c r="H25" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I25" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J25" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K25">
         <v>40</v>
       </c>
       <c r="L25" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M25" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N25" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O25" t="b">
         <v>0</v>
@@ -1811,40 +1844,40 @@
         <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E26" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F26">
-        <v>-305.85</v>
+        <v>2.26</v>
       </c>
       <c r="H26" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I26" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J26" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K26">
         <v>40</v>
       </c>
       <c r="L26" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M26" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N26" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O26" t="b">
         <v>0</v>
@@ -1858,40 +1891,40 @@
         <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E27" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G27">
-        <v>-115.4996999999999</v>
+        <v>5.73</v>
       </c>
       <c r="H27" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I27" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J27" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K27">
         <v>40</v>
       </c>
       <c r="L27" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M27" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N27" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
@@ -1905,40 +1938,40 @@
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E28" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F28">
-        <v>-403.5</v>
+        <v>0.04</v>
       </c>
       <c r="H28" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I28" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J28" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K28">
         <v>40</v>
       </c>
       <c r="L28" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M28" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N28" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O28" t="b">
         <v>0</v>
@@ -1952,40 +1985,40 @@
         <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E29" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G29">
-        <v>-70.09969999999993</v>
+        <v>0.86</v>
       </c>
       <c r="H29" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I29" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J29" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K29">
         <v>40</v>
       </c>
       <c r="L29" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M29" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N29" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O29" t="b">
         <v>0</v>
@@ -1999,40 +2032,40 @@
         <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E30" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F30">
-        <v>-386.6302</v>
+        <v>-305.85</v>
       </c>
       <c r="H30" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I30" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J30" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K30">
         <v>40</v>
       </c>
       <c r="L30" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M30" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N30" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O30" t="b">
         <v>0</v>
@@ -2046,40 +2079,40 @@
         <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G31">
-        <v>-7.169599999999918</v>
+        <v>-115.4996999999999</v>
       </c>
       <c r="H31" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I31" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J31" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K31">
         <v>40</v>
       </c>
       <c r="L31" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M31" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N31" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O31" t="b">
         <v>0</v>
@@ -2093,40 +2126,40 @@
         <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E32" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F32">
-        <v>-273.27</v>
+        <v>-403.5</v>
       </c>
       <c r="H32" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I32" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J32" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K32">
         <v>40</v>
       </c>
       <c r="L32" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M32" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N32" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O32" t="b">
         <v>0</v>
@@ -2140,40 +2173,40 @@
         <v>47</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E33" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G33">
-        <v>-131.07</v>
+        <v>-70.09969999999993</v>
       </c>
       <c r="H33" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I33" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J33" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K33">
         <v>40</v>
       </c>
       <c r="L33" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M33" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N33" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O33" t="b">
         <v>0</v>
@@ -2187,40 +2220,40 @@
         <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C34" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E34" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F34">
-        <v>-391.7</v>
+        <v>-386.6302</v>
       </c>
       <c r="H34" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I34" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J34" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K34">
         <v>40</v>
       </c>
       <c r="L34" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M34" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N34" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O34" t="b">
         <v>0</v>
@@ -2234,40 +2267,40 @@
         <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E35" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G35">
-        <v>-257.93</v>
+        <v>-7.169599999999918</v>
       </c>
       <c r="H35" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I35" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J35" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K35">
         <v>40</v>
       </c>
       <c r="L35" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M35" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N35" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O35" t="b">
         <v>0</v>
@@ -2281,40 +2314,40 @@
         <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D36" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E36" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F36">
-        <v>-461.67</v>
+        <v>-273.27</v>
       </c>
       <c r="H36" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I36" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J36" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K36">
         <v>40</v>
       </c>
       <c r="L36" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M36" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N36" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O36" t="b">
         <v>0</v>
@@ -2328,45 +2361,233 @@
         <v>51</v>
       </c>
       <c r="B37" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" t="s">
+        <v>78</v>
+      </c>
+      <c r="E37" t="s">
+        <v>85</v>
+      </c>
+      <c r="G37">
+        <v>-131.07</v>
+      </c>
+      <c r="H37" t="s">
+        <v>87</v>
+      </c>
+      <c r="I37" t="s">
+        <v>94</v>
+      </c>
+      <c r="J37" t="s">
+        <v>95</v>
+      </c>
+      <c r="K37">
+        <v>40</v>
+      </c>
+      <c r="L37" t="s">
+        <v>96</v>
+      </c>
+      <c r="M37" t="s">
+        <v>97</v>
+      </c>
+      <c r="N37" t="s">
+        <v>98</v>
+      </c>
+      <c r="O37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" t="s">
+        <v>85</v>
+      </c>
+      <c r="F38">
+        <v>-391.7</v>
+      </c>
+      <c r="H38" t="s">
+        <v>87</v>
+      </c>
+      <c r="I38" t="s">
+        <v>94</v>
+      </c>
+      <c r="J38" t="s">
+        <v>95</v>
+      </c>
+      <c r="K38">
+        <v>40</v>
+      </c>
+      <c r="L38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M38" t="s">
+        <v>97</v>
+      </c>
+      <c r="N38" t="s">
+        <v>98</v>
+      </c>
+      <c r="O38" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" t="s">
         <v>53</v>
       </c>
-      <c r="C37" t="s">
-        <v>69</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="B39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" t="s">
         <v>72</v>
       </c>
-      <c r="E37" t="s">
-        <v>77</v>
-      </c>
-      <c r="G37">
+      <c r="D39" t="s">
+        <v>78</v>
+      </c>
+      <c r="E39" t="s">
+        <v>85</v>
+      </c>
+      <c r="G39">
+        <v>-257.93</v>
+      </c>
+      <c r="H39" t="s">
+        <v>87</v>
+      </c>
+      <c r="I39" t="s">
+        <v>94</v>
+      </c>
+      <c r="J39" t="s">
+        <v>95</v>
+      </c>
+      <c r="K39">
+        <v>40</v>
+      </c>
+      <c r="L39" t="s">
+        <v>96</v>
+      </c>
+      <c r="M39" t="s">
+        <v>97</v>
+      </c>
+      <c r="N39" t="s">
+        <v>98</v>
+      </c>
+      <c r="O39" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" t="s">
+        <v>85</v>
+      </c>
+      <c r="F40">
+        <v>-461.67</v>
+      </c>
+      <c r="H40" t="s">
+        <v>87</v>
+      </c>
+      <c r="I40" t="s">
+        <v>94</v>
+      </c>
+      <c r="J40" t="s">
+        <v>95</v>
+      </c>
+      <c r="K40">
+        <v>40</v>
+      </c>
+      <c r="L40" t="s">
+        <v>96</v>
+      </c>
+      <c r="M40" t="s">
+        <v>97</v>
+      </c>
+      <c r="N40" t="s">
+        <v>98</v>
+      </c>
+      <c r="O40" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" t="s">
+        <v>73</v>
+      </c>
+      <c r="D41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E41" t="s">
+        <v>85</v>
+      </c>
+      <c r="G41">
         <v>-68.12969999999993</v>
       </c>
-      <c r="H37" t="s">
-        <v>79</v>
-      </c>
-      <c r="I37" t="s">
-        <v>83</v>
-      </c>
-      <c r="J37" t="s">
-        <v>84</v>
-      </c>
-      <c r="K37">
-        <v>40</v>
-      </c>
-      <c r="L37" t="s">
-        <v>85</v>
-      </c>
-      <c r="M37" t="s">
-        <v>86</v>
-      </c>
-      <c r="N37" t="s">
+      <c r="H41" t="s">
         <v>87</v>
       </c>
-      <c r="O37" t="b">
-        <v>0</v>
-      </c>
-      <c r="P37" t="b">
+      <c r="I41" t="s">
+        <v>94</v>
+      </c>
+      <c r="J41" t="s">
+        <v>95</v>
+      </c>
+      <c r="K41">
+        <v>40</v>
+      </c>
+      <c r="L41" t="s">
+        <v>96</v>
+      </c>
+      <c r="M41" t="s">
+        <v>97</v>
+      </c>
+      <c r="N41" t="s">
+        <v>98</v>
+      </c>
+      <c r="O41" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2377,7 +2598,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2435,16 +2656,16 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F2">
         <v>-0.2</v>
@@ -2453,22 +2674,22 @@
         <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -2482,16 +2703,16 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -2500,22 +2721,22 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
@@ -2526,43 +2747,43 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F4">
-        <v>-500</v>
+        <v>-0.2</v>
       </c>
       <c r="G4">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
@@ -2573,43 +2794,43 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F5">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="G5">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I5" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M5" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N5" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
@@ -2620,40 +2841,43 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>80</v>
+      </c>
+      <c r="F6">
+        <v>-400</v>
       </c>
       <c r="G6">
-        <v>0.15</v>
+        <v>200</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I6" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M6" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N6" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
@@ -2664,40 +2888,43 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>82</v>
+      </c>
+      <c r="F7">
+        <v>-1500</v>
       </c>
       <c r="G7">
-        <v>0.5</v>
+        <v>1500</v>
       </c>
       <c r="H7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I7" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N7" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -2708,40 +2935,40 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G8">
-        <v>8</v>
+        <v>0.15</v>
       </c>
       <c r="H8" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I8" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N8" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
@@ -2752,45 +2979,133 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G9">
+        <v>0.5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" t="s">
+        <v>90</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9" t="s">
+        <v>96</v>
+      </c>
+      <c r="M9" t="s">
+        <v>97</v>
+      </c>
+      <c r="N9" t="s">
+        <v>98</v>
+      </c>
+      <c r="O9" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+      <c r="H10" t="s">
+        <v>89</v>
+      </c>
+      <c r="I10" t="s">
+        <v>90</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10" t="s">
+        <v>96</v>
+      </c>
+      <c r="M10" t="s">
+        <v>97</v>
+      </c>
+      <c r="N10" t="s">
+        <v>98</v>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11">
         <v>25</v>
       </c>
-      <c r="H9" t="s">
-        <v>81</v>
-      </c>
-      <c r="I9" t="s">
-        <v>82</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9" t="s">
-        <v>85</v>
-      </c>
-      <c r="M9" t="s">
-        <v>86</v>
-      </c>
-      <c r="N9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O9" t="b">
-        <v>1</v>
-      </c>
-      <c r="P9" t="b">
+      <c r="H11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11" t="s">
+        <v>90</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11" t="s">
+        <v>96</v>
+      </c>
+      <c r="M11" t="s">
+        <v>97</v>
+      </c>
+      <c r="N11" t="s">
+        <v>98</v>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2856,43 +3171,43 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F2">
         <v>0.46</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K2">
         <v>40</v>
       </c>
       <c r="L2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
@@ -2903,43 +3218,43 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G3">
         <v>2.16</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I3" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J3" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K3">
         <v>40</v>
       </c>
       <c r="L3" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -2950,43 +3265,43 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F4">
         <v>0.59</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I4" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J4" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K4">
         <v>40</v>
       </c>
       <c r="L4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
@@ -2997,43 +3312,43 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G5">
         <v>2.58</v>
       </c>
       <c r="H5" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I5" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K5">
         <v>40</v>
       </c>
       <c r="L5" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M5" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N5" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
@@ -3044,43 +3359,43 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F6">
         <v>1.15</v>
       </c>
       <c r="H6" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I6" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J6" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K6">
         <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M6" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N6" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
@@ -3091,43 +3406,43 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G7">
         <v>3.95</v>
       </c>
       <c r="H7" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I7" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J7" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N7" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O7" t="b">
         <v>0</v>
@@ -3138,43 +3453,43 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F8">
         <v>-0.01</v>
       </c>
       <c r="H8" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I8" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J8" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K8">
         <v>40</v>
       </c>
       <c r="L8" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N8" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -3185,43 +3500,43 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G9">
         <v>0.6</v>
       </c>
       <c r="H9" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I9" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J9" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K9">
         <v>40</v>
       </c>
       <c r="L9" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N9" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
@@ -3232,43 +3547,43 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F10">
         <v>0.43</v>
       </c>
       <c r="H10" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I10" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J10" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K10">
         <v>40</v>
       </c>
       <c r="L10" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M10" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N10" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
@@ -3279,43 +3594,43 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G11">
         <v>2.13</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J11" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K11">
         <v>40</v>
       </c>
       <c r="L11" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M11" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N11" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O11" t="b">
         <v>0</v>
@@ -3326,43 +3641,43 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F12">
         <v>0.5600000000000001</v>
       </c>
       <c r="H12" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I12" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J12" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K12">
         <v>40</v>
       </c>
       <c r="L12" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M12" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N12" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
@@ -3373,43 +3688,43 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E13" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G13">
         <v>2.76</v>
       </c>
       <c r="H13" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J13" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K13">
         <v>40</v>
       </c>
       <c r="L13" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M13" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N13" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
@@ -3420,43 +3735,43 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F14">
         <v>2.26</v>
       </c>
       <c r="H14" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I14" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J14" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K14">
         <v>40</v>
       </c>
       <c r="L14" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M14" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N14" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
@@ -3467,43 +3782,43 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G15">
         <v>5.73</v>
       </c>
       <c r="H15" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J15" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K15">
         <v>40</v>
       </c>
       <c r="L15" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M15" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N15" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O15" t="b">
         <v>0</v>
@@ -3514,43 +3829,43 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F16">
         <v>0.04</v>
       </c>
       <c r="H16" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I16" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J16" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K16">
         <v>40</v>
       </c>
       <c r="L16" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M16" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N16" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O16" t="b">
         <v>0</v>
@@ -3561,43 +3876,43 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G17">
         <v>0.86</v>
       </c>
       <c r="H17" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I17" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J17" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K17">
         <v>40</v>
       </c>
       <c r="L17" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M17" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N17" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
@@ -3608,43 +3923,43 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F18">
         <v>-305.85</v>
       </c>
       <c r="H18" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I18" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J18" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K18">
         <v>40</v>
       </c>
       <c r="L18" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M18" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N18" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O18" t="b">
         <v>0</v>
@@ -3655,43 +3970,43 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G19">
         <v>-115.4996999999999</v>
       </c>
       <c r="H19" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I19" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J19" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K19">
         <v>40</v>
       </c>
       <c r="L19" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M19" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N19" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O19" t="b">
         <v>0</v>
@@ -3702,43 +4017,43 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F20">
         <v>-403.5</v>
       </c>
       <c r="H20" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I20" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J20" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K20">
         <v>40</v>
       </c>
       <c r="L20" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M20" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N20" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
@@ -3749,43 +4064,43 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G21">
         <v>-70.09969999999993</v>
       </c>
       <c r="H21" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I21" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J21" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K21">
         <v>40</v>
       </c>
       <c r="L21" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M21" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N21" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O21" t="b">
         <v>0</v>
@@ -3796,43 +4111,43 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F22">
         <v>-386.6302</v>
       </c>
       <c r="H22" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I22" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K22">
         <v>40</v>
       </c>
       <c r="L22" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M22" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N22" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
@@ -3843,43 +4158,43 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E23" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G23">
         <v>-7.169599999999918</v>
       </c>
       <c r="H23" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I23" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J23" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K23">
         <v>40</v>
       </c>
       <c r="L23" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M23" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N23" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O23" t="b">
         <v>0</v>
@@ -3890,43 +4205,43 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E24" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F24">
         <v>-273.27</v>
       </c>
       <c r="H24" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I24" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J24" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K24">
         <v>40</v>
       </c>
       <c r="L24" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M24" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N24" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O24" t="b">
         <v>0</v>
@@ -3937,43 +4252,43 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E25" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G25">
         <v>-131.07</v>
       </c>
       <c r="H25" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I25" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J25" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K25">
         <v>40</v>
       </c>
       <c r="L25" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M25" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N25" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O25" t="b">
         <v>0</v>
@@ -3984,43 +4299,43 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E26" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F26">
         <v>-391.7</v>
       </c>
       <c r="H26" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I26" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J26" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K26">
         <v>40</v>
       </c>
       <c r="L26" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M26" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N26" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O26" t="b">
         <v>0</v>
@@ -4031,43 +4346,43 @@
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E27" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G27">
         <v>-257.93</v>
       </c>
       <c r="H27" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I27" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J27" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K27">
         <v>40</v>
       </c>
       <c r="L27" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M27" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N27" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
@@ -4078,43 +4393,43 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E28" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F28">
         <v>-461.67</v>
       </c>
       <c r="H28" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I28" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J28" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K28">
         <v>40</v>
       </c>
       <c r="L28" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M28" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N28" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O28" t="b">
         <v>0</v>
@@ -4125,43 +4440,43 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E29" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G29">
         <v>-68.12969999999993</v>
       </c>
       <c r="H29" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I29" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J29" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K29">
         <v>40</v>
       </c>
       <c r="L29" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M29" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N29" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="O29" t="b">
         <v>0</v>

--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/data/D3_threshold_library.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/data/D3_threshold_library.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="103">
   <si>
     <t>threshold_id</t>
   </si>
@@ -186,6 +186,12 @@
     <t>T0040</t>
   </si>
   <si>
+    <t>T0041</t>
+  </si>
+  <si>
+    <t>T0042</t>
+  </si>
+  <si>
     <t>DO</t>
   </si>
   <si>
@@ -198,6 +204,12 @@
     <t>all_ORP</t>
   </si>
   <si>
+    <t>DO_1_4</t>
+  </si>
+  <si>
+    <t>DO_2_4</t>
+  </si>
+  <si>
     <t>DO_1_1</t>
   </si>
   <si>
@@ -207,9 +219,6 @@
     <t>DO_1_3</t>
   </si>
   <si>
-    <t>DO_1_4</t>
-  </si>
-  <si>
     <t>DO_2_1</t>
   </si>
   <si>
@@ -219,9 +228,6 @@
     <t>DO_2_3</t>
   </si>
   <si>
-    <t>DO_2_4</t>
-  </si>
-  <si>
     <t>ORP_1_1</t>
   </si>
   <si>
@@ -249,6 +255,9 @@
     <t>observed_values</t>
   </si>
   <si>
+    <t>post_anoxic</t>
+  </si>
+  <si>
     <t>contiguous_finite_observations</t>
   </si>
   <si>
@@ -288,7 +297,7 @@
     <t>mV/min</t>
   </si>
   <si>
-    <t>expert</t>
+    <t>provisional_expert_prior</t>
   </si>
   <si>
     <t>instrument_register</t>
@@ -300,6 +309,9 @@
     <t>registered_range</t>
   </si>
   <si>
+    <t>resolution_derived_provisional_zero_deadband</t>
+  </si>
+  <si>
     <t>benchmark_quantile</t>
   </si>
   <si>
@@ -309,10 +321,10 @@
     <t>benchmark@v2.2.0</t>
   </si>
   <si>
-    <t>fixed_physical_contract_v2.2.1</t>
-  </si>
-  <si>
-    <t>v2.2.1</t>
+    <t>physical_contract_v2.3.0</t>
+  </si>
+  <si>
+    <t>v2.3.0</t>
   </si>
 </sst>
 </file>
@@ -670,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -728,16 +740,16 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F2">
         <v>-0.2</v>
@@ -746,22 +758,22 @@
         <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -775,16 +787,16 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -793,22 +805,22 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
@@ -822,16 +834,16 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -840,22 +852,22 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
@@ -869,16 +881,16 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F5">
         <v>-0.2</v>
@@ -887,22 +899,22 @@
         <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
@@ -916,16 +928,16 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F6">
         <v>-500</v>
@@ -934,22 +946,22 @@
         <v>500</v>
       </c>
       <c r="H6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M6" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
@@ -963,16 +975,16 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F7">
         <v>-400</v>
@@ -981,22 +993,22 @@
         <v>200</v>
       </c>
       <c r="H7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N7" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -1010,16 +1022,16 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F8">
         <v>-1500</v>
@@ -1028,22 +1040,22 @@
         <v>1500</v>
       </c>
       <c r="H8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -1057,16 +1069,16 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F9">
         <v>-1500</v>
@@ -1075,22 +1087,22 @@
         <v>1500</v>
       </c>
       <c r="H9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N9" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
@@ -1104,37 +1116,40 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
         <v>83</v>
       </c>
+      <c r="F10">
+        <v>-0.05</v>
+      </c>
       <c r="G10">
-        <v>0.15</v>
+        <v>8</v>
       </c>
       <c r="H10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I10" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N10" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
@@ -1148,37 +1163,40 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>83</v>
+      </c>
+      <c r="F11">
+        <v>-0.05</v>
       </c>
       <c r="G11">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="H11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I11" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M11" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O11" t="b">
         <v>1</v>
@@ -1192,37 +1210,37 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G12">
-        <v>8</v>
+        <v>0.15</v>
       </c>
       <c r="H12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M12" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N12" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
@@ -1236,37 +1254,37 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G13">
-        <v>25</v>
+        <v>0.5</v>
       </c>
       <c r="H13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M13" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N13" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O13" t="b">
         <v>1</v>
@@ -1280,43 +1298,40 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
-      </c>
-      <c r="F14">
-        <v>0.46</v>
+        <v>86</v>
+      </c>
+      <c r="G14">
+        <v>8</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s">
-        <v>94</v>
-      </c>
-      <c r="J14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="b">
         <v>1</v>
@@ -1327,43 +1342,40 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G15">
-        <v>2.16</v>
+        <v>25</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s">
-        <v>94</v>
-      </c>
-      <c r="J15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M15" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="b">
         <v>1</v>
@@ -1374,40 +1386,40 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F16">
-        <v>0.59</v>
+        <v>0.46</v>
       </c>
       <c r="H16" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J16" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K16">
         <v>40</v>
       </c>
       <c r="L16" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M16" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O16" t="b">
         <v>0</v>
@@ -1421,40 +1433,40 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G17">
-        <v>2.58</v>
+        <v>2.16</v>
       </c>
       <c r="H17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I17" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J17" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K17">
         <v>40</v>
       </c>
       <c r="L17" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N17" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
@@ -1468,40 +1480,40 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F18">
-        <v>1.15</v>
+        <v>0.59</v>
       </c>
       <c r="H18" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I18" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J18" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K18">
         <v>40</v>
       </c>
       <c r="L18" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M18" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O18" t="b">
         <v>0</v>
@@ -1515,40 +1527,40 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G19">
-        <v>3.95</v>
+        <v>2.58</v>
       </c>
       <c r="H19" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J19" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K19">
         <v>40</v>
       </c>
       <c r="L19" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M19" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N19" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O19" t="b">
         <v>0</v>
@@ -1562,40 +1574,40 @@
         <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F20">
-        <v>-0.01</v>
+        <v>1.15</v>
       </c>
       <c r="H20" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I20" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J20" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K20">
         <v>40</v>
       </c>
       <c r="L20" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M20" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N20" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
@@ -1609,40 +1621,40 @@
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G21">
-        <v>0.6</v>
+        <v>3.95</v>
       </c>
       <c r="H21" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I21" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J21" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K21">
         <v>40</v>
       </c>
       <c r="L21" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M21" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N21" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O21" t="b">
         <v>0</v>
@@ -1656,40 +1668,40 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F22">
-        <v>0.43</v>
+        <v>-0.01</v>
       </c>
       <c r="H22" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I22" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J22" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K22">
         <v>40</v>
       </c>
       <c r="L22" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M22" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N22" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
@@ -1703,40 +1715,40 @@
         <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G23">
-        <v>2.13</v>
+        <v>0.6</v>
       </c>
       <c r="H23" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J23" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K23">
         <v>40</v>
       </c>
       <c r="L23" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M23" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N23" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O23" t="b">
         <v>0</v>
@@ -1750,40 +1762,40 @@
         <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F24">
-        <v>0.5600000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="H24" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J24" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K24">
         <v>40</v>
       </c>
       <c r="L24" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M24" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N24" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O24" t="b">
         <v>0</v>
@@ -1797,40 +1809,40 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G25">
-        <v>2.76</v>
+        <v>2.13</v>
       </c>
       <c r="H25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I25" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J25" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K25">
         <v>40</v>
       </c>
       <c r="L25" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M25" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N25" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O25" t="b">
         <v>0</v>
@@ -1844,40 +1856,40 @@
         <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F26">
-        <v>2.26</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H26" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I26" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J26" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K26">
         <v>40</v>
       </c>
       <c r="L26" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M26" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N26" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O26" t="b">
         <v>0</v>
@@ -1891,40 +1903,40 @@
         <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G27">
-        <v>5.73</v>
+        <v>2.76</v>
       </c>
       <c r="H27" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I27" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J27" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K27">
         <v>40</v>
       </c>
       <c r="L27" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M27" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N27" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
@@ -1938,40 +1950,40 @@
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F28">
-        <v>0.04</v>
+        <v>2.26</v>
       </c>
       <c r="H28" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I28" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J28" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K28">
         <v>40</v>
       </c>
       <c r="L28" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M28" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N28" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O28" t="b">
         <v>0</v>
@@ -1985,40 +1997,40 @@
         <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G29">
-        <v>0.86</v>
+        <v>5.73</v>
       </c>
       <c r="H29" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J29" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K29">
         <v>40</v>
       </c>
       <c r="L29" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M29" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N29" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O29" t="b">
         <v>0</v>
@@ -2032,40 +2044,40 @@
         <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F30">
-        <v>-305.85</v>
+        <v>0.04</v>
       </c>
       <c r="H30" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I30" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J30" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K30">
         <v>40</v>
       </c>
       <c r="L30" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M30" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N30" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O30" t="b">
         <v>0</v>
@@ -2079,40 +2091,40 @@
         <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E31" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G31">
-        <v>-115.4996999999999</v>
+        <v>0.86</v>
       </c>
       <c r="H31" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I31" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J31" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K31">
         <v>40</v>
       </c>
       <c r="L31" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M31" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N31" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O31" t="b">
         <v>0</v>
@@ -2126,40 +2138,40 @@
         <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D32" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E32" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F32">
-        <v>-403.5</v>
+        <v>-305.85</v>
       </c>
       <c r="H32" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I32" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J32" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K32">
         <v>40</v>
       </c>
       <c r="L32" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M32" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N32" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O32" t="b">
         <v>0</v>
@@ -2173,40 +2185,40 @@
         <v>47</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D33" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E33" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G33">
-        <v>-70.09969999999993</v>
+        <v>-115.4996999999999</v>
       </c>
       <c r="H33" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I33" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J33" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K33">
         <v>40</v>
       </c>
       <c r="L33" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M33" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N33" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O33" t="b">
         <v>0</v>
@@ -2220,40 +2232,40 @@
         <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D34" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E34" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F34">
-        <v>-386.6302</v>
+        <v>-403.5</v>
       </c>
       <c r="H34" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I34" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K34">
         <v>40</v>
       </c>
       <c r="L34" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N34" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O34" t="b">
         <v>0</v>
@@ -2267,40 +2279,40 @@
         <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D35" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E35" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G35">
-        <v>-7.169599999999918</v>
+        <v>-70.09969999999993</v>
       </c>
       <c r="H35" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I35" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J35" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K35">
         <v>40</v>
       </c>
       <c r="L35" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M35" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N35" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O35" t="b">
         <v>0</v>
@@ -2314,40 +2326,40 @@
         <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D36" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E36" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F36">
-        <v>-273.27</v>
+        <v>-386.6302</v>
       </c>
       <c r="H36" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I36" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J36" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K36">
         <v>40</v>
       </c>
       <c r="L36" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M36" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N36" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O36" t="b">
         <v>0</v>
@@ -2361,40 +2373,40 @@
         <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D37" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E37" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G37">
-        <v>-131.07</v>
+        <v>-7.169599999999918</v>
       </c>
       <c r="H37" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I37" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J37" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K37">
         <v>40</v>
       </c>
       <c r="L37" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M37" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N37" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O37" t="b">
         <v>0</v>
@@ -2408,40 +2420,40 @@
         <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D38" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E38" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F38">
-        <v>-391.7</v>
+        <v>-273.27</v>
       </c>
       <c r="H38" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I38" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J38" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K38">
         <v>40</v>
       </c>
       <c r="L38" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M38" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N38" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O38" t="b">
         <v>0</v>
@@ -2455,40 +2467,40 @@
         <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D39" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G39">
-        <v>-257.93</v>
+        <v>-131.07</v>
       </c>
       <c r="H39" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I39" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J39" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K39">
         <v>40</v>
       </c>
       <c r="L39" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M39" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N39" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O39" t="b">
         <v>0</v>
@@ -2502,40 +2514,40 @@
         <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D40" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E40" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F40">
-        <v>-461.67</v>
+        <v>-391.7</v>
       </c>
       <c r="H40" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I40" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J40" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K40">
         <v>40</v>
       </c>
       <c r="L40" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M40" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N40" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O40" t="b">
         <v>0</v>
@@ -2549,45 +2561,139 @@
         <v>55</v>
       </c>
       <c r="B41" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" t="s">
+        <v>88</v>
+      </c>
+      <c r="G41">
+        <v>-257.93</v>
+      </c>
+      <c r="H41" t="s">
+        <v>90</v>
+      </c>
+      <c r="I41" t="s">
+        <v>98</v>
+      </c>
+      <c r="J41" t="s">
+        <v>99</v>
+      </c>
+      <c r="K41">
+        <v>40</v>
+      </c>
+      <c r="L41" t="s">
+        <v>100</v>
+      </c>
+      <c r="M41" t="s">
+        <v>101</v>
+      </c>
+      <c r="N41" t="s">
+        <v>102</v>
+      </c>
+      <c r="O41" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" t="s">
+        <v>81</v>
+      </c>
+      <c r="E42" t="s">
+        <v>88</v>
+      </c>
+      <c r="F42">
+        <v>-461.67</v>
+      </c>
+      <c r="H42" t="s">
+        <v>90</v>
+      </c>
+      <c r="I42" t="s">
+        <v>98</v>
+      </c>
+      <c r="J42" t="s">
+        <v>99</v>
+      </c>
+      <c r="K42">
+        <v>40</v>
+      </c>
+      <c r="L42" t="s">
+        <v>100</v>
+      </c>
+      <c r="M42" t="s">
+        <v>101</v>
+      </c>
+      <c r="N42" t="s">
+        <v>102</v>
+      </c>
+      <c r="O42" t="b">
+        <v>0</v>
+      </c>
+      <c r="P42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" t="s">
         <v>57</v>
       </c>
-      <c r="C41" t="s">
-        <v>73</v>
-      </c>
-      <c r="D41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E41" t="s">
-        <v>85</v>
-      </c>
-      <c r="G41">
+      <c r="B43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" t="s">
+        <v>75</v>
+      </c>
+      <c r="D43" t="s">
+        <v>81</v>
+      </c>
+      <c r="E43" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43">
         <v>-68.12969999999993</v>
       </c>
-      <c r="H41" t="s">
-        <v>87</v>
-      </c>
-      <c r="I41" t="s">
-        <v>94</v>
-      </c>
-      <c r="J41" t="s">
-        <v>95</v>
-      </c>
-      <c r="K41">
-        <v>40</v>
-      </c>
-      <c r="L41" t="s">
-        <v>96</v>
-      </c>
-      <c r="M41" t="s">
-        <v>97</v>
-      </c>
-      <c r="N41" t="s">
-        <v>98</v>
-      </c>
-      <c r="O41" t="b">
-        <v>0</v>
-      </c>
-      <c r="P41" t="b">
+      <c r="H43" t="s">
+        <v>90</v>
+      </c>
+      <c r="I43" t="s">
+        <v>98</v>
+      </c>
+      <c r="J43" t="s">
+        <v>99</v>
+      </c>
+      <c r="K43">
+        <v>40</v>
+      </c>
+      <c r="L43" t="s">
+        <v>100</v>
+      </c>
+      <c r="M43" t="s">
+        <v>101</v>
+      </c>
+      <c r="N43" t="s">
+        <v>102</v>
+      </c>
+      <c r="O43" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2598,7 +2704,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2656,16 +2762,16 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F2">
         <v>-0.2</v>
@@ -2674,22 +2780,22 @@
         <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -2703,16 +2809,16 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -2721,22 +2827,22 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
@@ -2750,16 +2856,16 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F4">
         <v>-0.2</v>
@@ -2768,22 +2874,22 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
@@ -2797,16 +2903,16 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F5">
         <v>-500</v>
@@ -2815,22 +2921,22 @@
         <v>500</v>
       </c>
       <c r="H5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
@@ -2844,16 +2950,16 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F6">
         <v>-400</v>
@@ -2862,22 +2968,22 @@
         <v>200</v>
       </c>
       <c r="H6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M6" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
@@ -2891,16 +2997,16 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F7">
         <v>-1500</v>
@@ -2909,22 +3015,22 @@
         <v>1500</v>
       </c>
       <c r="H7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N7" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -2938,37 +3044,40 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>83</v>
       </c>
+      <c r="F8">
+        <v>-0.05</v>
+      </c>
       <c r="G8">
-        <v>0.15</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I8" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
@@ -2982,37 +3091,40 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>83</v>
+      </c>
+      <c r="F9">
+        <v>-0.05</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="H9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I9" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N9" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
@@ -3026,37 +3138,37 @@
         <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G10">
-        <v>8</v>
+        <v>0.15</v>
       </c>
       <c r="H10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N10" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
@@ -3070,42 +3182,130 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11">
+        <v>0.5</v>
+      </c>
+      <c r="H11" t="s">
+        <v>91</v>
+      </c>
+      <c r="I11" t="s">
+        <v>93</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11" t="s">
+        <v>100</v>
+      </c>
+      <c r="M11" t="s">
+        <v>101</v>
+      </c>
+      <c r="N11" t="s">
+        <v>102</v>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
         <v>59</v>
       </c>
-      <c r="D11" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" t="s">
-        <v>84</v>
-      </c>
-      <c r="G11">
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12">
+        <v>8</v>
+      </c>
+      <c r="H12" t="s">
+        <v>92</v>
+      </c>
+      <c r="I12" t="s">
+        <v>93</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12" t="s">
+        <v>100</v>
+      </c>
+      <c r="M12" t="s">
+        <v>101</v>
+      </c>
+      <c r="N12" t="s">
+        <v>102</v>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13">
         <v>25</v>
       </c>
-      <c r="H11" t="s">
-        <v>89</v>
-      </c>
-      <c r="I11" t="s">
-        <v>90</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11" t="s">
-        <v>96</v>
-      </c>
-      <c r="M11" t="s">
-        <v>97</v>
-      </c>
-      <c r="N11" t="s">
-        <v>98</v>
-      </c>
-      <c r="O11" t="b">
-        <v>1</v>
-      </c>
-      <c r="P11" t="b">
+      <c r="H13" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" t="s">
+        <v>93</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13" t="s">
+        <v>100</v>
+      </c>
+      <c r="M13" t="s">
+        <v>101</v>
+      </c>
+      <c r="N13" t="s">
+        <v>102</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3171,43 +3371,43 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F2">
         <v>0.46</v>
       </c>
       <c r="H2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K2">
         <v>40</v>
       </c>
       <c r="L2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
@@ -3218,43 +3418,43 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G3">
         <v>2.16</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K3">
         <v>40</v>
       </c>
       <c r="L3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -3265,43 +3465,43 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F4">
         <v>0.59</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K4">
         <v>40</v>
       </c>
       <c r="L4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
@@ -3312,43 +3512,43 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G5">
         <v>2.58</v>
       </c>
       <c r="H5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K5">
         <v>40</v>
       </c>
       <c r="L5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
@@ -3359,43 +3559,43 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F6">
         <v>1.15</v>
       </c>
       <c r="H6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K6">
         <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M6" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
@@ -3406,43 +3606,43 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G7">
         <v>3.95</v>
       </c>
       <c r="H7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N7" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O7" t="b">
         <v>0</v>
@@ -3453,43 +3653,43 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F8">
         <v>-0.01</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K8">
         <v>40</v>
       </c>
       <c r="L8" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -3500,43 +3700,43 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G9">
         <v>0.6</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I9" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J9" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K9">
         <v>40</v>
       </c>
       <c r="L9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N9" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
@@ -3547,43 +3747,43 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F10">
         <v>0.43</v>
       </c>
       <c r="H10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K10">
         <v>40</v>
       </c>
       <c r="L10" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N10" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
@@ -3594,43 +3794,43 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G11">
         <v>2.13</v>
       </c>
       <c r="H11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J11" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K11">
         <v>40</v>
       </c>
       <c r="L11" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M11" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O11" t="b">
         <v>0</v>
@@ -3641,43 +3841,43 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F12">
         <v>0.5600000000000001</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K12">
         <v>40</v>
       </c>
       <c r="L12" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M12" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N12" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
@@ -3688,43 +3888,43 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G13">
         <v>2.76</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K13">
         <v>40</v>
       </c>
       <c r="L13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M13" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N13" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
@@ -3735,43 +3935,43 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F14">
         <v>2.26</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I14" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J14" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K14">
         <v>40</v>
       </c>
       <c r="L14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
@@ -3782,43 +3982,43 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G15">
         <v>5.73</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J15" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K15">
         <v>40</v>
       </c>
       <c r="L15" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M15" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O15" t="b">
         <v>0</v>
@@ -3829,43 +4029,43 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F16">
         <v>0.04</v>
       </c>
       <c r="H16" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J16" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K16">
         <v>40</v>
       </c>
       <c r="L16" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M16" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O16" t="b">
         <v>0</v>
@@ -3876,43 +4076,43 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G17">
         <v>0.86</v>
       </c>
       <c r="H17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I17" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J17" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K17">
         <v>40</v>
       </c>
       <c r="L17" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N17" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
@@ -3923,43 +4123,43 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F18">
         <v>-305.85</v>
       </c>
       <c r="H18" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I18" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J18" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K18">
         <v>40</v>
       </c>
       <c r="L18" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M18" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O18" t="b">
         <v>0</v>
@@ -3970,43 +4170,43 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G19">
         <v>-115.4996999999999</v>
       </c>
       <c r="H19" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I19" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J19" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K19">
         <v>40</v>
       </c>
       <c r="L19" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M19" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N19" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O19" t="b">
         <v>0</v>
@@ -4017,43 +4217,43 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F20">
         <v>-403.5</v>
       </c>
       <c r="H20" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I20" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J20" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K20">
         <v>40</v>
       </c>
       <c r="L20" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M20" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N20" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
@@ -4064,43 +4264,43 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G21">
         <v>-70.09969999999993</v>
       </c>
       <c r="H21" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I21" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J21" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K21">
         <v>40</v>
       </c>
       <c r="L21" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M21" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N21" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O21" t="b">
         <v>0</v>
@@ -4111,43 +4311,43 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F22">
         <v>-386.6302</v>
       </c>
       <c r="H22" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I22" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J22" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K22">
         <v>40</v>
       </c>
       <c r="L22" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M22" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N22" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
@@ -4158,43 +4358,43 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G23">
         <v>-7.169599999999918</v>
       </c>
       <c r="H23" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J23" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K23">
         <v>40</v>
       </c>
       <c r="L23" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M23" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N23" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O23" t="b">
         <v>0</v>
@@ -4205,43 +4405,43 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F24">
         <v>-273.27</v>
       </c>
       <c r="H24" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I24" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J24" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K24">
         <v>40</v>
       </c>
       <c r="L24" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M24" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N24" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O24" t="b">
         <v>0</v>
@@ -4252,43 +4452,43 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G25">
         <v>-131.07</v>
       </c>
       <c r="H25" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I25" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J25" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K25">
         <v>40</v>
       </c>
       <c r="L25" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M25" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N25" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O25" t="b">
         <v>0</v>
@@ -4299,43 +4499,43 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F26">
         <v>-391.7</v>
       </c>
       <c r="H26" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I26" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J26" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K26">
         <v>40</v>
       </c>
       <c r="L26" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M26" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N26" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O26" t="b">
         <v>0</v>
@@ -4346,43 +4546,43 @@
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G27">
         <v>-257.93</v>
       </c>
       <c r="H27" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J27" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K27">
         <v>40</v>
       </c>
       <c r="L27" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M27" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N27" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
@@ -4393,43 +4593,43 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F28">
         <v>-461.67</v>
       </c>
       <c r="H28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I28" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J28" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K28">
         <v>40</v>
       </c>
       <c r="L28" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M28" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N28" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O28" t="b">
         <v>0</v>
@@ -4440,43 +4640,43 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G29">
         <v>-68.12969999999993</v>
       </c>
       <c r="H29" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I29" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J29" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K29">
         <v>40</v>
       </c>
       <c r="L29" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M29" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N29" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O29" t="b">
         <v>0</v>

--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/data/D3_threshold_library.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/data/D3_threshold_library.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="107">
   <si>
     <t>threshold_id</t>
   </si>
@@ -192,6 +192,12 @@
     <t>T0042</t>
   </si>
   <si>
+    <t>T0043</t>
+  </si>
+  <si>
+    <t>T0044</t>
+  </si>
+  <si>
     <t>DO</t>
   </si>
   <si>
@@ -276,6 +282,9 @@
     <t>instrument_veto</t>
   </si>
   <si>
+    <t>zero_equivalence</t>
+  </si>
+  <si>
     <t>rate_soft</t>
   </si>
   <si>
@@ -309,7 +318,10 @@
     <t>registered_range</t>
   </si>
   <si>
-    <t>resolution_derived_provisional_zero_deadband</t>
+    <t>sensor_specific_physical_and_operational_contract</t>
+  </si>
+  <si>
+    <t>resolution_derived_provisional_zero_point_tolerance</t>
   </si>
   <si>
     <t>benchmark_quantile</t>
@@ -321,10 +333,10 @@
     <t>benchmark@v2.2.0</t>
   </si>
   <si>
-    <t>physical_contract_v2.3.0</t>
-  </si>
-  <si>
-    <t>v2.3.0</t>
+    <t>physical_contract_v2.4.0</t>
+  </si>
+  <si>
+    <t>v2.4.0</t>
   </si>
 </sst>
 </file>
@@ -682,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -740,16 +752,16 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F2">
         <v>-0.2</v>
@@ -758,22 +770,22 @@
         <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -787,16 +799,16 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -805,22 +817,22 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
@@ -834,16 +846,16 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -852,22 +864,22 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
@@ -881,16 +893,16 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F5">
         <v>-0.2</v>
@@ -899,22 +911,22 @@
         <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
@@ -928,16 +940,16 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F6">
         <v>-500</v>
@@ -946,22 +958,22 @@
         <v>500</v>
       </c>
       <c r="H6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
@@ -975,16 +987,16 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F7">
         <v>-400</v>
@@ -993,22 +1005,22 @@
         <v>200</v>
       </c>
       <c r="H7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M7" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -1022,16 +1034,16 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F8">
         <v>-1500</v>
@@ -1040,22 +1052,22 @@
         <v>1500</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -1069,16 +1081,16 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F9">
         <v>-1500</v>
@@ -1087,22 +1099,22 @@
         <v>1500</v>
       </c>
       <c r="H9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
@@ -1116,40 +1128,37 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F10">
-        <v>-0.05</v>
-      </c>
-      <c r="G10">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M10" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N10" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
@@ -1163,40 +1172,40 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F11">
         <v>-0.05</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M11" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O11" t="b">
         <v>1</v>
@@ -1210,37 +1219,37 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
-      </c>
-      <c r="G12">
-        <v>0.15</v>
+        <v>85</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I12" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M12" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
@@ -1254,37 +1263,40 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="F13">
+        <v>-0.05</v>
       </c>
       <c r="G13">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I13" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M13" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N13" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O13" t="b">
         <v>1</v>
@@ -1298,37 +1310,37 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G14">
-        <v>8</v>
+        <v>0.15</v>
       </c>
       <c r="H14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O14" t="b">
         <v>1</v>
@@ -1342,37 +1354,37 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G15">
-        <v>25</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I15" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M15" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N15" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O15" t="b">
         <v>1</v>
@@ -1386,43 +1398,40 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16">
-        <v>0.46</v>
+        <v>89</v>
+      </c>
+      <c r="G16">
+        <v>8</v>
       </c>
       <c r="H16" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s">
-        <v>98</v>
-      </c>
-      <c r="J16" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K16">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M16" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N16" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" t="b">
         <v>1</v>
@@ -1433,43 +1442,40 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G17">
-        <v>2.16</v>
+        <v>25</v>
       </c>
       <c r="H17" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I17" t="s">
-        <v>98</v>
-      </c>
-      <c r="J17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K17">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M17" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N17" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" t="b">
         <v>1</v>
@@ -1480,40 +1486,40 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F18">
-        <v>0.59</v>
+        <v>0.46</v>
       </c>
       <c r="H18" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K18">
         <v>40</v>
       </c>
       <c r="L18" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N18" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O18" t="b">
         <v>0</v>
@@ -1527,40 +1533,40 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G19">
-        <v>2.58</v>
+        <v>2.16</v>
       </c>
       <c r="H19" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I19" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J19" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K19">
         <v>40</v>
       </c>
       <c r="L19" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M19" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O19" t="b">
         <v>0</v>
@@ -1574,40 +1580,40 @@
         <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F20">
-        <v>1.15</v>
+        <v>0.59</v>
       </c>
       <c r="H20" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J20" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K20">
         <v>40</v>
       </c>
       <c r="L20" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M20" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N20" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
@@ -1621,40 +1627,40 @@
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G21">
-        <v>3.95</v>
+        <v>2.58</v>
       </c>
       <c r="H21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I21" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J21" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K21">
         <v>40</v>
       </c>
       <c r="L21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M21" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N21" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O21" t="b">
         <v>0</v>
@@ -1668,40 +1674,40 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F22">
-        <v>-0.01</v>
+        <v>1.15</v>
       </c>
       <c r="H22" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I22" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J22" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K22">
         <v>40</v>
       </c>
       <c r="L22" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M22" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
@@ -1715,40 +1721,40 @@
         <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G23">
-        <v>0.6</v>
+        <v>3.95</v>
       </c>
       <c r="H23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J23" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K23">
         <v>40</v>
       </c>
       <c r="L23" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M23" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N23" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O23" t="b">
         <v>0</v>
@@ -1762,40 +1768,40 @@
         <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F24">
-        <v>0.43</v>
+        <v>-0.01</v>
       </c>
       <c r="H24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I24" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J24" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K24">
         <v>40</v>
       </c>
       <c r="L24" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M24" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N24" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O24" t="b">
         <v>0</v>
@@ -1809,40 +1815,40 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E25" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G25">
-        <v>2.13</v>
+        <v>0.6</v>
       </c>
       <c r="H25" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I25" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J25" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K25">
         <v>40</v>
       </c>
       <c r="L25" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M25" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O25" t="b">
         <v>0</v>
@@ -1856,40 +1862,40 @@
         <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F26">
-        <v>0.5600000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="H26" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I26" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J26" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K26">
         <v>40</v>
       </c>
       <c r="L26" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M26" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N26" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O26" t="b">
         <v>0</v>
@@ -1903,40 +1909,40 @@
         <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E27" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G27">
-        <v>2.76</v>
+        <v>2.13</v>
       </c>
       <c r="H27" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I27" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J27" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K27">
         <v>40</v>
       </c>
       <c r="L27" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M27" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N27" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
@@ -1950,40 +1956,40 @@
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F28">
-        <v>2.26</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H28" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I28" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J28" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K28">
         <v>40</v>
       </c>
       <c r="L28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M28" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N28" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O28" t="b">
         <v>0</v>
@@ -1997,40 +2003,40 @@
         <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E29" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G29">
-        <v>5.73</v>
+        <v>2.76</v>
       </c>
       <c r="H29" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I29" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J29" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K29">
         <v>40</v>
       </c>
       <c r="L29" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M29" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N29" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O29" t="b">
         <v>0</v>
@@ -2044,40 +2050,40 @@
         <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E30" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F30">
-        <v>0.04</v>
+        <v>2.26</v>
       </c>
       <c r="H30" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I30" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J30" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K30">
         <v>40</v>
       </c>
       <c r="L30" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M30" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N30" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O30" t="b">
         <v>0</v>
@@ -2091,40 +2097,40 @@
         <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E31" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G31">
-        <v>0.86</v>
+        <v>5.73</v>
       </c>
       <c r="H31" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I31" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J31" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K31">
         <v>40</v>
       </c>
       <c r="L31" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M31" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N31" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O31" t="b">
         <v>0</v>
@@ -2138,40 +2144,40 @@
         <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F32">
-        <v>-305.85</v>
+        <v>0.04</v>
       </c>
       <c r="H32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I32" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J32" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K32">
         <v>40</v>
       </c>
       <c r="L32" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M32" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N32" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O32" t="b">
         <v>0</v>
@@ -2185,40 +2191,40 @@
         <v>47</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E33" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G33">
-        <v>-115.4996999999999</v>
+        <v>0.86</v>
       </c>
       <c r="H33" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I33" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J33" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K33">
         <v>40</v>
       </c>
       <c r="L33" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M33" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N33" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O33" t="b">
         <v>0</v>
@@ -2232,40 +2238,40 @@
         <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D34" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F34">
-        <v>-403.5</v>
+        <v>-305.85</v>
       </c>
       <c r="H34" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I34" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J34" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K34">
         <v>40</v>
       </c>
       <c r="L34" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M34" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N34" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O34" t="b">
         <v>0</v>
@@ -2279,40 +2285,40 @@
         <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G35">
-        <v>-70.09969999999993</v>
+        <v>-115.4996999999999</v>
       </c>
       <c r="H35" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I35" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J35" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K35">
         <v>40</v>
       </c>
       <c r="L35" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M35" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N35" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O35" t="b">
         <v>0</v>
@@ -2326,40 +2332,40 @@
         <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E36" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F36">
-        <v>-386.6302</v>
+        <v>-403.5</v>
       </c>
       <c r="H36" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I36" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J36" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K36">
         <v>40</v>
       </c>
       <c r="L36" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M36" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N36" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O36" t="b">
         <v>0</v>
@@ -2373,40 +2379,40 @@
         <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D37" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E37" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G37">
-        <v>-7.169599999999918</v>
+        <v>-70.09969999999993</v>
       </c>
       <c r="H37" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I37" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J37" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K37">
         <v>40</v>
       </c>
       <c r="L37" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M37" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N37" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O37" t="b">
         <v>0</v>
@@ -2420,40 +2426,40 @@
         <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D38" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E38" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F38">
-        <v>-273.27</v>
+        <v>-386.6302</v>
       </c>
       <c r="H38" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I38" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J38" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K38">
         <v>40</v>
       </c>
       <c r="L38" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M38" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N38" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O38" t="b">
         <v>0</v>
@@ -2467,40 +2473,40 @@
         <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D39" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E39" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G39">
-        <v>-131.07</v>
+        <v>-7.169599999999918</v>
       </c>
       <c r="H39" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I39" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J39" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K39">
         <v>40</v>
       </c>
       <c r="L39" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M39" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N39" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O39" t="b">
         <v>0</v>
@@ -2514,40 +2520,40 @@
         <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D40" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E40" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F40">
-        <v>-391.7</v>
+        <v>-273.27</v>
       </c>
       <c r="H40" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I40" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J40" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K40">
         <v>40</v>
       </c>
       <c r="L40" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M40" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N40" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O40" t="b">
         <v>0</v>
@@ -2561,40 +2567,40 @@
         <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D41" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E41" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G41">
-        <v>-257.93</v>
+        <v>-131.07</v>
       </c>
       <c r="H41" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I41" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J41" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K41">
         <v>40</v>
       </c>
       <c r="L41" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M41" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N41" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O41" t="b">
         <v>0</v>
@@ -2608,40 +2614,40 @@
         <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D42" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E42" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F42">
-        <v>-461.67</v>
+        <v>-391.7</v>
       </c>
       <c r="H42" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I42" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J42" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K42">
         <v>40</v>
       </c>
       <c r="L42" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M42" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N42" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O42" t="b">
         <v>0</v>
@@ -2655,45 +2661,139 @@
         <v>57</v>
       </c>
       <c r="B43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" t="s">
+        <v>76</v>
+      </c>
+      <c r="D43" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" t="s">
+        <v>91</v>
+      </c>
+      <c r="G43">
+        <v>-257.93</v>
+      </c>
+      <c r="H43" t="s">
+        <v>93</v>
+      </c>
+      <c r="I43" t="s">
+        <v>102</v>
+      </c>
+      <c r="J43" t="s">
+        <v>103</v>
+      </c>
+      <c r="K43">
+        <v>40</v>
+      </c>
+      <c r="L43" t="s">
+        <v>104</v>
+      </c>
+      <c r="M43" t="s">
+        <v>105</v>
+      </c>
+      <c r="N43" t="s">
+        <v>106</v>
+      </c>
+      <c r="O43" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" t="s">
+        <v>77</v>
+      </c>
+      <c r="D44" t="s">
+        <v>83</v>
+      </c>
+      <c r="E44" t="s">
+        <v>91</v>
+      </c>
+      <c r="F44">
+        <v>-461.67</v>
+      </c>
+      <c r="H44" t="s">
+        <v>93</v>
+      </c>
+      <c r="I44" t="s">
+        <v>102</v>
+      </c>
+      <c r="J44" t="s">
+        <v>103</v>
+      </c>
+      <c r="K44">
+        <v>40</v>
+      </c>
+      <c r="L44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M44" t="s">
+        <v>105</v>
+      </c>
+      <c r="N44" t="s">
+        <v>106</v>
+      </c>
+      <c r="O44" t="b">
+        <v>0</v>
+      </c>
+      <c r="P44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" t="s">
         <v>59</v>
       </c>
-      <c r="C43" t="s">
-        <v>75</v>
-      </c>
-      <c r="D43" t="s">
-        <v>81</v>
-      </c>
-      <c r="E43" t="s">
-        <v>88</v>
-      </c>
-      <c r="G43">
+      <c r="B45" t="s">
+        <v>61</v>
+      </c>
+      <c r="C45" t="s">
+        <v>77</v>
+      </c>
+      <c r="D45" t="s">
+        <v>83</v>
+      </c>
+      <c r="E45" t="s">
+        <v>91</v>
+      </c>
+      <c r="G45">
         <v>-68.12969999999993</v>
       </c>
-      <c r="H43" t="s">
-        <v>90</v>
-      </c>
-      <c r="I43" t="s">
-        <v>98</v>
-      </c>
-      <c r="J43" t="s">
-        <v>99</v>
-      </c>
-      <c r="K43">
-        <v>40</v>
-      </c>
-      <c r="L43" t="s">
-        <v>100</v>
-      </c>
-      <c r="M43" t="s">
-        <v>101</v>
-      </c>
-      <c r="N43" t="s">
-        <v>102</v>
-      </c>
-      <c r="O43" t="b">
-        <v>0</v>
-      </c>
-      <c r="P43" t="b">
+      <c r="H45" t="s">
+        <v>93</v>
+      </c>
+      <c r="I45" t="s">
+        <v>102</v>
+      </c>
+      <c r="J45" t="s">
+        <v>103</v>
+      </c>
+      <c r="K45">
+        <v>40</v>
+      </c>
+      <c r="L45" t="s">
+        <v>104</v>
+      </c>
+      <c r="M45" t="s">
+        <v>105</v>
+      </c>
+      <c r="N45" t="s">
+        <v>106</v>
+      </c>
+      <c r="O45" t="b">
+        <v>0</v>
+      </c>
+      <c r="P45" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2704,7 +2804,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2762,16 +2862,16 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F2">
         <v>-0.2</v>
@@ -2780,22 +2880,22 @@
         <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -2809,16 +2909,16 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -2827,22 +2927,22 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
@@ -2856,16 +2956,16 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F4">
         <v>-0.2</v>
@@ -2874,22 +2974,22 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
@@ -2903,16 +3003,16 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F5">
         <v>-500</v>
@@ -2921,22 +3021,22 @@
         <v>500</v>
       </c>
       <c r="H5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
@@ -2950,16 +3050,16 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F6">
         <v>-400</v>
@@ -2968,22 +3068,22 @@
         <v>200</v>
       </c>
       <c r="H6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
@@ -2997,16 +3097,16 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F7">
         <v>-1500</v>
@@ -3015,22 +3115,22 @@
         <v>1500</v>
       </c>
       <c r="H7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M7" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -3044,40 +3144,37 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F8">
-        <v>-0.05</v>
-      </c>
-      <c r="G8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
@@ -3091,40 +3188,40 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F9">
         <v>-0.05</v>
       </c>
       <c r="G9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
@@ -3138,37 +3235,37 @@
         <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>86</v>
-      </c>
-      <c r="G10">
-        <v>0.15</v>
+        <v>85</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M10" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N10" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
@@ -3182,37 +3279,40 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="F11">
+        <v>-0.05</v>
       </c>
       <c r="G11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M11" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O11" t="b">
         <v>1</v>
@@ -3226,37 +3326,37 @@
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G12">
-        <v>8</v>
+        <v>0.15</v>
       </c>
       <c r="H12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I12" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M12" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
@@ -3270,42 +3370,130 @@
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13">
+        <v>0.5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13" t="s">
+        <v>104</v>
+      </c>
+      <c r="M13" t="s">
+        <v>105</v>
+      </c>
+      <c r="N13" t="s">
+        <v>106</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
         <v>61</v>
       </c>
-      <c r="D13" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13">
+      <c r="C14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14">
+        <v>8</v>
+      </c>
+      <c r="H14" t="s">
+        <v>95</v>
+      </c>
+      <c r="I14" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14" t="s">
+        <v>104</v>
+      </c>
+      <c r="M14" t="s">
+        <v>105</v>
+      </c>
+      <c r="N14" t="s">
+        <v>106</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15">
         <v>25</v>
       </c>
-      <c r="H13" t="s">
-        <v>92</v>
-      </c>
-      <c r="I13" t="s">
-        <v>93</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13" t="s">
-        <v>100</v>
-      </c>
-      <c r="M13" t="s">
-        <v>101</v>
-      </c>
-      <c r="N13" t="s">
-        <v>102</v>
-      </c>
-      <c r="O13" t="b">
-        <v>1</v>
-      </c>
-      <c r="P13" t="b">
+      <c r="H15" t="s">
+        <v>95</v>
+      </c>
+      <c r="I15" t="s">
+        <v>96</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15" t="s">
+        <v>104</v>
+      </c>
+      <c r="M15" t="s">
+        <v>105</v>
+      </c>
+      <c r="N15" t="s">
+        <v>106</v>
+      </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3371,43 +3559,43 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F2">
         <v>0.46</v>
       </c>
       <c r="H2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K2">
         <v>40</v>
       </c>
       <c r="L2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
@@ -3418,43 +3606,43 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G3">
         <v>2.16</v>
       </c>
       <c r="H3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K3">
         <v>40</v>
       </c>
       <c r="L3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -3465,43 +3653,43 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F4">
         <v>0.59</v>
       </c>
       <c r="H4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K4">
         <v>40</v>
       </c>
       <c r="L4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
@@ -3512,43 +3700,43 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G5">
         <v>2.58</v>
       </c>
       <c r="H5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K5">
         <v>40</v>
       </c>
       <c r="L5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
@@ -3559,43 +3747,43 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F6">
         <v>1.15</v>
       </c>
       <c r="H6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K6">
         <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
@@ -3606,43 +3794,43 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G7">
         <v>3.95</v>
       </c>
       <c r="H7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I7" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M7" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O7" t="b">
         <v>0</v>
@@ -3653,43 +3841,43 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F8">
         <v>-0.01</v>
       </c>
       <c r="H8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J8" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K8">
         <v>40</v>
       </c>
       <c r="L8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -3700,43 +3888,43 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G9">
         <v>0.6</v>
       </c>
       <c r="H9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K9">
         <v>40</v>
       </c>
       <c r="L9" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
@@ -3747,43 +3935,43 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F10">
         <v>0.43</v>
       </c>
       <c r="H10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K10">
         <v>40</v>
       </c>
       <c r="L10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M10" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N10" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
@@ -3794,43 +3982,43 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G11">
         <v>2.13</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K11">
         <v>40</v>
       </c>
       <c r="L11" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M11" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O11" t="b">
         <v>0</v>
@@ -3841,43 +4029,43 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F12">
         <v>0.5600000000000001</v>
       </c>
       <c r="H12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I12" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K12">
         <v>40</v>
       </c>
       <c r="L12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M12" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
@@ -3888,43 +4076,43 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G13">
         <v>2.76</v>
       </c>
       <c r="H13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I13" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J13" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K13">
         <v>40</v>
       </c>
       <c r="L13" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M13" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N13" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
@@ -3935,43 +4123,43 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F14">
         <v>2.26</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K14">
         <v>40</v>
       </c>
       <c r="L14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
@@ -3982,43 +4170,43 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G15">
         <v>5.73</v>
       </c>
       <c r="H15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J15" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K15">
         <v>40</v>
       </c>
       <c r="L15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M15" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N15" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O15" t="b">
         <v>0</v>
@@ -4029,43 +4217,43 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F16">
         <v>0.04</v>
       </c>
       <c r="H16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J16" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K16">
         <v>40</v>
       </c>
       <c r="L16" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M16" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N16" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O16" t="b">
         <v>0</v>
@@ -4076,43 +4264,43 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G17">
         <v>0.86</v>
       </c>
       <c r="H17" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J17" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K17">
         <v>40</v>
       </c>
       <c r="L17" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M17" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N17" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
@@ -4123,43 +4311,43 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F18">
         <v>-305.85</v>
       </c>
       <c r="H18" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K18">
         <v>40</v>
       </c>
       <c r="L18" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N18" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O18" t="b">
         <v>0</v>
@@ -4170,43 +4358,43 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G19">
         <v>-115.4996999999999</v>
       </c>
       <c r="H19" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I19" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J19" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K19">
         <v>40</v>
       </c>
       <c r="L19" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M19" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O19" t="b">
         <v>0</v>
@@ -4217,43 +4405,43 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F20">
         <v>-403.5</v>
       </c>
       <c r="H20" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I20" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J20" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K20">
         <v>40</v>
       </c>
       <c r="L20" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M20" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N20" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
@@ -4264,43 +4452,43 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G21">
         <v>-70.09969999999993</v>
       </c>
       <c r="H21" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I21" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J21" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K21">
         <v>40</v>
       </c>
       <c r="L21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M21" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N21" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O21" t="b">
         <v>0</v>
@@ -4311,43 +4499,43 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F22">
         <v>-386.6302</v>
       </c>
       <c r="H22" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I22" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J22" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K22">
         <v>40</v>
       </c>
       <c r="L22" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M22" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
@@ -4358,43 +4546,43 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G23">
         <v>-7.169599999999918</v>
       </c>
       <c r="H23" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I23" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J23" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K23">
         <v>40</v>
       </c>
       <c r="L23" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M23" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N23" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O23" t="b">
         <v>0</v>
@@ -4405,43 +4593,43 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F24">
         <v>-273.27</v>
       </c>
       <c r="H24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I24" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J24" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K24">
         <v>40</v>
       </c>
       <c r="L24" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M24" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N24" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O24" t="b">
         <v>0</v>
@@ -4452,43 +4640,43 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E25" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G25">
         <v>-131.07</v>
       </c>
       <c r="H25" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I25" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J25" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K25">
         <v>40</v>
       </c>
       <c r="L25" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M25" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O25" t="b">
         <v>0</v>
@@ -4499,43 +4687,43 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F26">
         <v>-391.7</v>
       </c>
       <c r="H26" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I26" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J26" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K26">
         <v>40</v>
       </c>
       <c r="L26" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M26" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N26" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O26" t="b">
         <v>0</v>
@@ -4546,43 +4734,43 @@
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E27" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G27">
         <v>-257.93</v>
       </c>
       <c r="H27" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I27" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J27" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K27">
         <v>40</v>
       </c>
       <c r="L27" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M27" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N27" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
@@ -4593,43 +4781,43 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F28">
         <v>-461.67</v>
       </c>
       <c r="H28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I28" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J28" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K28">
         <v>40</v>
       </c>
       <c r="L28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M28" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N28" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O28" t="b">
         <v>0</v>
@@ -4640,43 +4828,43 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E29" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G29">
         <v>-68.12969999999993</v>
       </c>
       <c r="H29" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I29" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J29" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K29">
         <v>40</v>
       </c>
       <c r="L29" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M29" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N29" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O29" t="b">
         <v>0</v>

--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/data/D3_threshold_library.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/data/D3_threshold_library.xlsx
@@ -333,10 +333,10 @@
     <t>benchmark@v2.2.0</t>
   </si>
   <si>
-    <t>physical_contract_v2.4.0</t>
-  </si>
-  <si>
-    <t>v2.4.0</t>
+    <t>physical_contract_v2.5.0</t>
+  </si>
+  <si>
+    <t>v2.5.0</t>
   </si>
 </sst>
 </file>
@@ -813,9 +813,6 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3">
-        <v>8</v>
-      </c>
       <c r="H3" t="s">
         <v>92</v>
       </c>
@@ -2923,9 +2920,6 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3">
-        <v>8</v>
-      </c>
       <c r="H3" t="s">
         <v>92</v>
       </c>

--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/data/D3_threshold_library.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/data/D3_threshold_library.xlsx
@@ -333,10 +333,10 @@
     <t>benchmark@v2.2.0</t>
   </si>
   <si>
-    <t>physical_contract_v2.5.0</t>
-  </si>
-  <si>
-    <t>v2.5.0</t>
+    <t>physical_contract_v2.6.0</t>
+  </si>
+  <si>
+    <t>v2.6.0</t>
   </si>
 </sst>
 </file>

--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/data/D3_threshold_library.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/data/D3_threshold_library.xlsx
@@ -333,10 +333,10 @@
     <t>benchmark@v2.2.0</t>
   </si>
   <si>
-    <t>physical_contract_v2.6.0</t>
-  </si>
-  <si>
-    <t>v2.6.0</t>
+    <t>physical_contract_v2.7.0</t>
+  </si>
+  <si>
+    <t>v2.7.0</t>
   </si>
 </sst>
 </file>
